--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/NEW_YORK_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/NEW_YORK_2023.xlsx
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C226">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1119">
